--- a/output/pdf_financials_xlsx/CERT.xlsx
+++ b/output/pdf_financials_xlsx/CERT.xlsx
@@ -3371,22 +3371,22 @@
         <v>0.045</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.658</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.443</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>6.679</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.943</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.082</v>
       </c>
     </row>
     <row r="93">
@@ -6816,7 +6816,11 @@
           <t>Share-based payment reserve 23</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -10174,7 +10178,11 @@
           <t>Share-based payment reserve 22</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -11010,7 +11018,11 @@
           <t>Share-based payment reserve 20</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -12344,7 +12356,11 @@
           <t>Share-based payment reserve 19</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -12804,7 +12820,11 @@
           <t>Share-based payment reserve 6</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CERT.xlsx
+++ b/output/pdf_financials_xlsx/CERT.xlsx
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.825493</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.741763</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>6.638</v>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.825493</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.741763</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>6.663</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.825493</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.741763</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>5.101</v>
@@ -12416,7 +12416,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -13056,7 +13056,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">

--- a/output/pdf_financials_xlsx/CERT.xlsx
+++ b/output/pdf_financials_xlsx/CERT.xlsx
@@ -832,13 +832,13 @@
         <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>-4.517</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>-6.129</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>-8.096</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>-0</v>
@@ -1318,13 +1318,13 @@
         <v>-0.077821</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-11.879</v>
+        <v>-7.362</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.697</v>
+        <v>1.432</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.355</v>
+        <v>7.741</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>5.148</v>
@@ -1380,13 +1380,13 @@
         <v>-0.077821</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-11.879</v>
+        <v>-7.362</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.697</v>
+        <v>1.432</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.355</v>
+        <v>7.741</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>5.148</v>
@@ -28312,7 +28312,11 @@
           <t>Net finance expense $</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CERT.xlsx
+++ b/output/pdf_financials_xlsx/CERT.xlsx
@@ -510,43 +510,29 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D4" s="3" t="n">
+        <v>32.194</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>70.051</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>90.36</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>100.101</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>116.169</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>147.085</v>
       </c>
     </row>
     <row r="5">
@@ -586,43 +572,29 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D6" s="3" t="n">
+        <v>32.194</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>70.051</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>90.36</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>100.101</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>116.169</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>147.085</v>
       </c>
     </row>
     <row r="7">
@@ -755,28 +727,20 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.008002</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.016438</v>
       </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D11" s="3" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>70.048</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>90.15900000000001</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0.845</v>
@@ -965,7 +929,7 @@
         <v>5.09</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-7.289</v>
+        <v>10.153</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>2.608</v>
@@ -1414,35 +1378,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D30" s="3" t="n">
+        <v>-22.86761508355594</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>2.044224921842658</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>8.566843736166446</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>5.142805766176163</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>20.01480601537416</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>-28.04704762552266</v>
       </c>
     </row>
     <row r="31">
@@ -1467,7 +1419,7 @@
         <v>-622.2493887530562</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>214.3823529411765</v>
+        <v>298.6176470588235</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>11.44311350971875</v>
@@ -1492,35 +1444,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D32" s="3" t="n">
+        <v>-39.04143629247686</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>-8.992020099641691</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>-6.538291279327135</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>-6.746186351784697</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>21.86383630744863</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>-13.86817146547915</v>
       </c>
     </row>
     <row r="33">
@@ -2586,22 +2526,22 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>9.076000000000001</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>11.005</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>21.047</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>14.168</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="68">
@@ -2620,19 +2560,19 @@
         <v>0.013447</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>21.9</v>
+        <v>30.976</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>24.1</v>
+        <v>35.105</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>40.765</v>
+        <v>61.812</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>29.221</v>
+        <v>43.389</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>37.107</v>
+        <v>51.707</v>
       </c>
     </row>
     <row r="69">
@@ -2679,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.408</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="F70" s="3" t="n">
         <v>0</v>
@@ -2710,10 +2650,10 @@
         <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.408</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>6.706</v>
+        <v>7.397</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>2.061</v>
@@ -2834,22 +2774,22 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>21.558553</v>
+        <v>21.150553</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>28.478</v>
+        <v>18.711</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>50.035</v>
+        <v>39.03</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>100.553</v>
+        <v>79.506</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>88.791</v>
+        <v>74.623</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>136.256</v>
+        <v>121.656</v>
       </c>
     </row>
     <row r="76">
@@ -2992,13 +2932,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D80" s="3" t="n">
+        <v>0.09805335255948089</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.5290966803332893</v>
+        <v>0.5747916942203413</v>
       </c>
       <c r="F80" s="3" t="n">
         <v>0.3064999251160701</v>
@@ -4268,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-0.094</v>
       </c>
       <c r="I121" s="3" t="n">
         <v>0</v>
@@ -4552,10 +4490,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>-0.014766</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0.825493</v>
@@ -4647,10 +4583,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.825493</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>0.741763</v>
@@ -4753,7 +4687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L465"/>
+  <dimension ref="A1:L470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11918,7 +11852,11 @@
           <t>Lease obligations 12</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -16278,7 +16216,11 @@
           <t>Share repurchase</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -20108,7 +20050,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -23638,7 +23584,11 @@
           <t>Private Placement</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E343" s="5" t="n">
         <v>1</v>
       </c>
@@ -23913,66 +23863,84 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>REVENUES</t>
+          <t>activities</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Metal sales $</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr"/>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E348" s="5" t="n">
+        <v>0.045</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G348" s="5" t="n">
-        <v>32.194</v>
-      </c>
-      <c r="H348" s="5" t="n">
-        <v>70.051</v>
-      </c>
-      <c r="I348" s="5" t="n">
-        <v>90.36</v>
-      </c>
-      <c r="J348" s="5" t="n">
-        <v>100.101</v>
-      </c>
-      <c r="K348" s="5" t="n">
-        <v>116.169</v>
-      </c>
-      <c r="L348" s="5" t="n">
-        <v>147.085</v>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Production costs</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr"/>
+          <t>Cash, beginning of the period</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -23983,69 +23951,95 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G349" s="5" t="n">
-        <v>24.853</v>
-      </c>
-      <c r="H349" s="5" t="n">
-        <v>43.234</v>
-      </c>
-      <c r="I349" s="5" t="n">
-        <v>53.07</v>
-      </c>
-      <c r="J349" s="5" t="n">
-        <v>66.777</v>
-      </c>
-      <c r="K349" s="5" t="n">
-        <v>82.063</v>
-      </c>
-      <c r="L349" s="5" t="n">
-        <v>84.89</v>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Sales expenses and royalties</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr"/>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of the period $</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E350" s="5" t="n">
+        <v>0.825493</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G350" s="5" t="n">
-        <v>4.094</v>
-      </c>
-      <c r="H350" s="5" t="n">
-        <v>7.392</v>
-      </c>
-      <c r="I350" s="5" t="n">
-        <v>9.436</v>
-      </c>
-      <c r="J350" s="5" t="n">
-        <v>10.231</v>
-      </c>
-      <c r="K350" s="5" t="n">
-        <v>3.828</v>
-      </c>
-      <c r="L350" s="5" t="n">
-        <v>4.963</v>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="351">
@@ -24056,15 +24050,19 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>REVENUES</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Depreciation and depletion</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr"/>
+          <t>Metal sales $</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -24076,22 +24074,22 @@
         </is>
       </c>
       <c r="G351" s="5" t="n">
-        <v>2.504</v>
+        <v>32.194</v>
       </c>
       <c r="H351" s="5" t="n">
-        <v>5.724</v>
+        <v>70.051</v>
       </c>
       <c r="I351" s="5" t="n">
-        <v>8.395</v>
+        <v>90.36</v>
       </c>
       <c r="J351" s="5" t="n">
-        <v>9.273999999999999</v>
+        <v>100.101</v>
       </c>
       <c r="K351" s="5" t="n">
-        <v>20.279</v>
+        <v>116.169</v>
       </c>
       <c r="L351" s="5" t="n">
-        <v>25.409</v>
+        <v>147.085</v>
       </c>
     </row>
     <row r="352">
@@ -24107,14 +24105,10 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>INCOME FROM MINING OPERATIONS</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>NetIncomeContinuousOperations</t>
-        </is>
-      </c>
+          <t>Production costs</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
         <is>
           <t>-</t>
@@ -24126,22 +24120,22 @@
         </is>
       </c>
       <c r="G352" s="5" t="n">
-        <v>0.743</v>
+        <v>24.853</v>
       </c>
       <c r="H352" s="5" t="n">
-        <v>13.701</v>
+        <v>43.234</v>
       </c>
       <c r="I352" s="5" t="n">
-        <v>19.459</v>
+        <v>53.07</v>
       </c>
       <c r="J352" s="5" t="n">
-        <v>13.819</v>
+        <v>66.777</v>
       </c>
       <c r="K352" s="5" t="n">
-        <v>9.999000000000001</v>
+        <v>82.063</v>
       </c>
       <c r="L352" s="5" t="n">
-        <v>31.823</v>
+        <v>84.89</v>
       </c>
     </row>
     <row r="353">
@@ -24157,14 +24151,10 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>General and administrative expenses 24</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Sales expenses and royalties</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
           <t>-</t>
@@ -24175,29 +24165,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G353" s="5" t="n">
+        <v>4.094</v>
+      </c>
+      <c r="H353" s="5" t="n">
+        <v>7.392</v>
+      </c>
+      <c r="I353" s="5" t="n">
+        <v>9.436</v>
       </c>
       <c r="J353" s="5" t="n">
-        <v>12.974</v>
+        <v>10.231</v>
       </c>
       <c r="K353" s="5" t="n">
-        <v>10.836</v>
+        <v>3.828</v>
       </c>
       <c r="L353" s="5" t="n">
-        <v>12.507</v>
+        <v>4.963</v>
       </c>
     </row>
     <row r="354">
@@ -24213,14 +24197,10 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>INCOME (LOSS) BEFORE OTHER ITEMS</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Depreciation and depletion</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -24231,29 +24211,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I354" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G354" s="5" t="n">
+        <v>2.504</v>
+      </c>
+      <c r="H354" s="5" t="n">
+        <v>5.724</v>
+      </c>
+      <c r="I354" s="5" t="n">
+        <v>8.395</v>
       </c>
       <c r="J354" s="5" t="n">
-        <v>0.845</v>
+        <v>9.273999999999999</v>
       </c>
       <c r="K354" s="5" t="n">
-        <v>-0.837</v>
+        <v>20.279</v>
       </c>
       <c r="L354" s="5" t="n">
-        <v>19.316</v>
+        <v>25.409</v>
       </c>
     </row>
     <row r="355">
@@ -24269,12 +24243,12 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Finance income 25</t>
+          <t>INCOME FROM MINING OPERATIONS</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>NetIncomeContinuousOperations</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -24287,29 +24261,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G355" s="5" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="H355" s="5" t="n">
+        <v>13.701</v>
+      </c>
+      <c r="I355" s="5" t="n">
+        <v>19.459</v>
       </c>
       <c r="J355" s="5" t="n">
-        <v>-1.748</v>
+        <v>13.819</v>
       </c>
       <c r="K355" s="5" t="n">
-        <v>-0.46</v>
+        <v>9.999000000000001</v>
       </c>
       <c r="L355" s="5" t="n">
-        <v>-2.485</v>
+        <v>31.823</v>
       </c>
     </row>
     <row r="356">
@@ -24325,10 +24293,14 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Finance expense 25</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>General and administrative expenses 24</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -24355,13 +24327,13 @@
         </is>
       </c>
       <c r="J356" s="5" t="n">
-        <v>7.832</v>
+        <v>12.974</v>
       </c>
       <c r="K356" s="5" t="n">
-        <v>7.902</v>
+        <v>10.836</v>
       </c>
       <c r="L356" s="5" t="n">
-        <v>6.372</v>
+        <v>12.507</v>
       </c>
     </row>
     <row r="357">
@@ -24377,12 +24349,12 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
+          <t>INCOME (LOSS) BEFORE OTHER ITEMS</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -24411,13 +24383,13 @@
         </is>
       </c>
       <c r="J357" s="5" t="n">
-        <v>-10.306</v>
+        <v>0.845</v>
       </c>
       <c r="K357" s="5" t="n">
-        <v>-10.2</v>
+        <v>-0.837</v>
       </c>
       <c r="L357" s="5" t="n">
-        <v>-3.949</v>
+        <v>19.316</v>
       </c>
     </row>
     <row r="358">
@@ -24433,10 +24405,14 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Remeasurement of Ascendant secured note and stream obligation 16</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr"/>
+          <t>Finance income 25</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -24462,18 +24438,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J358" s="5" t="n">
+        <v>-1.748</v>
+      </c>
+      <c r="K358" s="5" t="n">
+        <v>-0.46</v>
       </c>
       <c r="L358" s="5" t="n">
-        <v>7.173</v>
+        <v>-2.485</v>
       </c>
     </row>
     <row r="359">
@@ -24489,7 +24461,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Remeasurement of MDN stream obligation 15</t>
+          <t>Finance expense 25</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
@@ -24519,13 +24491,13 @@
         </is>
       </c>
       <c r="J359" s="5" t="n">
-        <v>-4.5</v>
+        <v>7.832</v>
       </c>
       <c r="K359" s="5" t="n">
-        <v>1.744</v>
+        <v>7.902</v>
       </c>
       <c r="L359" s="5" t="n">
-        <v>8.005000000000001</v>
+        <v>6.372</v>
       </c>
     </row>
     <row r="360">
@@ -24541,10 +24513,14 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Other expense (income)</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr"/>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>-</t>
@@ -24555,11 +24531,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G360" s="5" t="n">
-        <v>-1.086</v>
-      </c>
-      <c r="H360" s="5" t="n">
-        <v>1.56</v>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
@@ -24567,13 +24547,13 @@
         </is>
       </c>
       <c r="J360" s="5" t="n">
-        <v>1.562</v>
+        <v>-10.306</v>
       </c>
       <c r="K360" s="5" t="n">
-        <v>-2.965</v>
+        <v>-10.2</v>
       </c>
       <c r="L360" s="5" t="n">
-        <v>1.258</v>
+        <v>-3.949</v>
       </c>
     </row>
     <row r="361">
@@ -24589,7 +24569,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>OTHER LOSS (INCOME)</t>
+          <t>Remeasurement of Ascendant secured note and stream obligation 16</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
@@ -24623,11 +24603,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K361" s="5" t="n">
-        <v>-3.979</v>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L361" s="5" t="n">
-        <v>16.374</v>
+        <v>7.173</v>
       </c>
     </row>
     <row r="362">
@@ -24643,14 +24625,10 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>INCOME FROM CONTINUING OPERATIONS BEFORE INCOME TAXES $</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Remeasurement of MDN stream obligation 15</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -24677,13 +24655,13 @@
         </is>
       </c>
       <c r="J362" s="5" t="n">
-        <v>7.289</v>
+        <v>-4.5</v>
       </c>
       <c r="K362" s="5" t="n">
-        <v>3.142</v>
+        <v>1.744</v>
       </c>
       <c r="L362" s="5" t="n">
-        <v>2.942</v>
+        <v>8.005000000000001</v>
       </c>
     </row>
     <row r="363">
@@ -24699,7 +24677,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Income and mining tax expense 31</t>
+          <t>Other expense (income)</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -24713,31 +24691,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H363" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G363" s="5" t="n">
+        <v>-1.086</v>
+      </c>
+      <c r="H363" s="5" t="n">
+        <v>1.56</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J363" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J363" s="5" t="n">
+        <v>1.562</v>
       </c>
       <c r="K363" s="5" t="n">
-        <v>-2.658</v>
+        <v>-2.965</v>
       </c>
       <c r="L363" s="5" t="n">
-        <v>-17.693</v>
+        <v>1.258</v>
       </c>
     </row>
     <row r="364">
@@ -24753,7 +24725,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Deferred recovery (expense) 31</t>
+          <t>OTHER LOSS (INCOME)</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -24788,10 +24760,10 @@
         </is>
       </c>
       <c r="K364" s="5" t="n">
-        <v>0.05</v>
+        <v>-3.979</v>
       </c>
       <c r="L364" s="5" t="n">
-        <v>-5.647</v>
+        <v>16.374</v>
       </c>
     </row>
     <row r="365">
@@ -24807,7 +24779,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>INCOME FROM CONTINUING OPERATIONS BEFORE INCOME TAXES $</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -24840,16 +24812,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J365" s="5" t="n">
+        <v>7.289</v>
       </c>
       <c r="K365" s="5" t="n">
-        <v>-2.608</v>
+        <v>3.142</v>
       </c>
       <c r="L365" s="5" t="n">
-        <v>-23.34</v>
+        <v>2.942</v>
       </c>
     </row>
     <row r="366">
@@ -24865,7 +24835,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Net income (loss) from continuing operations for the year $</t>
+          <t>Income and mining tax expense 31</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -24894,14 +24864,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J366" s="5" t="n">
-        <v>-2.864</v>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K366" s="5" t="n">
-        <v>0.534</v>
+        <v>-2.658</v>
       </c>
       <c r="L366" s="5" t="n">
-        <v>-20.398</v>
+        <v>-17.693</v>
       </c>
     </row>
     <row r="367">
@@ -24917,7 +24889,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Net income from discountinued operations for the year $</t>
+          <t>Deferred recovery (expense) 31</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -24952,12 +24924,10 @@
         </is>
       </c>
       <c r="K367" s="5" t="n">
-        <v>24.865</v>
-      </c>
-      <c r="L367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.05</v>
+      </c>
+      <c r="L367" s="5" t="n">
+        <v>-5.647</v>
       </c>
     </row>
     <row r="368">
@@ -24973,12 +24943,12 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Total net income (loss) for the year $</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -25012,10 +24982,10 @@
         </is>
       </c>
       <c r="K368" s="5" t="n">
-        <v>25.399</v>
+        <v>-2.608</v>
       </c>
       <c r="L368" s="5" t="n">
-        <v>-20.398</v>
+        <v>-23.34</v>
       </c>
     </row>
     <row r="369">
@@ -25026,12 +24996,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE INCOME (LOSS)</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Translation adjustment $</t>
+          <t>Net income (loss) from continuing operations for the year $</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -25050,20 +25020,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H369" s="5" t="n">
-        <v>-1.367</v>
-      </c>
-      <c r="I369" s="5" t="n">
-        <v>1.076</v>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J369" s="5" t="n">
-        <v>3.52</v>
+        <v>-2.864</v>
       </c>
       <c r="K369" s="5" t="n">
-        <v>-0.282</v>
+        <v>0.534</v>
       </c>
       <c r="L369" s="5" t="n">
-        <v>2.656</v>
+        <v>-20.398</v>
       </c>
     </row>
     <row r="370">
@@ -25074,12 +25048,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE INCOME (LOSS)</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Net income from discountinued operations for the year $</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -25098,20 +25072,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H370" s="5" t="n">
-        <v>-1.367</v>
-      </c>
-      <c r="I370" s="5" t="n">
-        <v>1.076</v>
-      </c>
-      <c r="J370" s="5" t="n">
-        <v>3.52</v>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K370" s="5" t="n">
-        <v>-0.282</v>
-      </c>
-      <c r="L370" s="5" t="n">
-        <v>2.656</v>
+        <v>24.865</v>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="371">
@@ -25122,15 +25104,19 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE INCOME (LOSS)</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Total comprehensive income (loss) $</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr"/>
+          <t>Total net income (loss) for the year $</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -25146,20 +25132,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H371" s="5" t="n">
-        <v>-7.666</v>
-      </c>
-      <c r="I371" s="5" t="n">
-        <v>-4.832</v>
-      </c>
-      <c r="J371" s="5" t="n">
-        <v>-3.233</v>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K371" s="5" t="n">
-        <v>25.117</v>
+        <v>25.399</v>
       </c>
       <c r="L371" s="5" t="n">
-        <v>-17.742</v>
+        <v>-20.398</v>
       </c>
     </row>
     <row r="372">
@@ -25170,12 +25162,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>OTHER COMPREHENSIVE INCOME (LOSS)</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Equity holders of the parent $</t>
+          <t>Translation adjustment $</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
@@ -25194,26 +25186,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H372" s="5" t="n">
+        <v>-1.367</v>
+      </c>
+      <c r="I372" s="5" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="J372" s="5" t="n">
+        <v>3.52</v>
       </c>
       <c r="K372" s="5" t="n">
-        <v>25.117</v>
+        <v>-0.282</v>
       </c>
       <c r="L372" s="5" t="n">
-        <v>-17.594</v>
+        <v>2.656</v>
       </c>
     </row>
     <row r="373">
@@ -25224,19 +25210,15 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>OTHER COMPREHENSIVE INCOME (LOSS)</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Non-controlling interest</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -25252,28 +25234,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H373" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I373" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J373" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K373" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H373" s="5" t="n">
+        <v>-1.367</v>
+      </c>
+      <c r="I373" s="5" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="J373" s="5" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="K373" s="5" t="n">
+        <v>-0.282</v>
       </c>
       <c r="L373" s="5" t="n">
-        <v>0.148</v>
+        <v>2.656</v>
       </c>
     </row>
     <row r="374">
@@ -25284,7 +25258,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Attributable to</t>
+          <t>OTHER COMPREHENSIVE INCOME (LOSS)</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -25308,20 +25282,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H374" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I374" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J374" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H374" s="5" t="n">
+        <v>-7.666</v>
+      </c>
+      <c r="I374" s="5" t="n">
+        <v>-4.832</v>
+      </c>
+      <c r="J374" s="5" t="n">
+        <v>-3.233</v>
       </c>
       <c r="K374" s="5" t="n">
         <v>25.117</v>
@@ -25343,7 +25311,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Basic and diluted income (loss) per share from continuing operations $</t>
+          <t>Equity holders of the parent $</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -25378,10 +25346,10 @@
         </is>
       </c>
       <c r="K375" s="5" t="n">
-        <v>1e-08</v>
+        <v>25.117</v>
       </c>
       <c r="L375" s="5" t="n">
-        <v>-1.7e-07</v>
+        <v>-17.594</v>
       </c>
     </row>
     <row r="376">
@@ -25397,10 +25365,14 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Basic $</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr"/>
+          <t>Non-controlling interest</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -25431,13 +25403,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K376" s="5" t="n">
-        <v>0.00024</v>
-      </c>
-      <c r="L376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L376" s="5" t="n">
+        <v>0.148</v>
       </c>
     </row>
     <row r="377">
@@ -25453,7 +25425,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Diluted $</t>
+          <t>Total comprehensive income (loss) $</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -25488,12 +25460,10 @@
         </is>
       </c>
       <c r="K377" s="5" t="n">
-        <v>0.00023</v>
-      </c>
-      <c r="L377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>25.117</v>
+      </c>
+      <c r="L377" s="5" t="n">
+        <v>-17.742</v>
       </c>
     </row>
     <row r="378">
@@ -25509,7 +25479,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Basic and diluted income (loss) per share from continuing operations $</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
@@ -25544,10 +25514,10 @@
         </is>
       </c>
       <c r="K378" s="5" t="n">
-        <v>101921.092</v>
+        <v>1e-08</v>
       </c>
       <c r="L378" s="5" t="n">
-        <v>122990.498</v>
+        <v>-1.7e-07</v>
       </c>
     </row>
     <row r="379">
@@ -25563,7 +25533,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Diluted</t>
+          <t>Basic $</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
@@ -25598,10 +25568,12 @@
         </is>
       </c>
       <c r="K379" s="5" t="n">
-        <v>106023.171</v>
-      </c>
-      <c r="L379" s="5" t="n">
-        <v>122990.498</v>
+        <v>0.00024</v>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="380">
@@ -25612,12 +25584,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Transaction costs 20</t>
+          <t>Diluted $</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -25646,11 +25618,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J380" s="5" t="n">
-        <v>0.716</v>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K380" s="5" t="n">
-        <v>0.145</v>
+        <v>0.00023</v>
       </c>
       <c r="L380" t="inlineStr">
         <is>
@@ -25666,19 +25640,15 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>OTHER INCOME</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
           <t>-</t>
@@ -25704,16 +25674,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J381" s="5" t="n">
-        <v>-6.444</v>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K381" s="5" t="n">
-        <v>-3.979</v>
-      </c>
-      <c r="L381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>101921.092</v>
+      </c>
+      <c r="L381" s="5" t="n">
+        <v>122990.498</v>
       </c>
     </row>
     <row r="382">
@@ -25724,12 +25694,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>Attributable to</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Income and mining tax expense</t>
+          <t>Diluted</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -25753,19 +25723,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I382" s="5" t="n">
-        <v>-2.081</v>
-      </c>
-      <c r="J382" s="5" t="n">
-        <v>-2.452</v>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K382" s="5" t="n">
-        <v>-2.658</v>
-      </c>
-      <c r="L382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>106023.171</v>
+      </c>
+      <c r="L382" s="5" t="n">
+        <v>122990.498</v>
       </c>
     </row>
     <row r="383">
@@ -25781,7 +25753,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Deferred tax recovery (expense) 31</t>
+          <t>Transaction costs 20</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -25811,10 +25783,10 @@
         </is>
       </c>
       <c r="J383" s="5" t="n">
-        <v>-7.701</v>
+        <v>0.716</v>
       </c>
       <c r="K383" s="5" t="n">
-        <v>0.05</v>
+        <v>0.145</v>
       </c>
       <c r="L383" t="inlineStr">
         <is>
@@ -25835,10 +25807,14 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense) 31</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>OTHER INCOME</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -25865,10 +25841,10 @@
         </is>
       </c>
       <c r="J384" s="5" t="n">
-        <v>-10.153</v>
+        <v>-6.444</v>
       </c>
       <c r="K384" s="5" t="n">
-        <v>-2.608</v>
+        <v>-3.979</v>
       </c>
       <c r="L384" t="inlineStr">
         <is>
@@ -25889,7 +25865,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Net income (loss) from discountinued operations for the year $</t>
+          <t>Income and mining tax expense</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -25913,16 +25889,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I385" s="5" t="n">
+        <v>-2.081</v>
       </c>
       <c r="J385" s="5" t="n">
-        <v>-3.889</v>
+        <v>-2.452</v>
       </c>
       <c r="K385" s="5" t="n">
-        <v>24.865</v>
+        <v>-2.658</v>
       </c>
       <c r="L385" t="inlineStr">
         <is>
@@ -25938,12 +25912,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE INCOME (LOSS)</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Basic $</t>
+          <t>Deferred tax recovery (expense) 31</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -25973,10 +25947,10 @@
         </is>
       </c>
       <c r="J386" s="5" t="n">
-        <v>-3e-05</v>
+        <v>-7.701</v>
       </c>
       <c r="K386" s="5" t="n">
-        <v>1e-05</v>
+        <v>0.05</v>
       </c>
       <c r="L386" t="inlineStr">
         <is>
@@ -25992,15 +25966,19 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE INCOME (LOSS)</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Diluted $</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr"/>
+          <t>Income tax recovery (expense) 31</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -26027,10 +26005,10 @@
         </is>
       </c>
       <c r="J387" s="5" t="n">
-        <v>-3e-05</v>
+        <v>-10.153</v>
       </c>
       <c r="K387" s="5" t="n">
-        <v>1e-05</v>
+        <v>-2.608</v>
       </c>
       <c r="L387" t="inlineStr">
         <is>
@@ -26046,19 +26024,15 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Net income (loss) from discountinued operations for the year $</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -26074,17 +26048,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H388" s="5" t="n">
-        <v>69.93377099999999</v>
-      </c>
-      <c r="I388" s="5" t="n">
-        <v>77.521216</v>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J388" s="5" t="n">
-        <v>89.725553</v>
+        <v>-3.889</v>
       </c>
       <c r="K388" s="5" t="n">
-        <v>101.921092</v>
+        <v>24.865</v>
       </c>
       <c r="L388" t="inlineStr">
         <is>
@@ -26100,19 +26078,15 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>OTHER COMPREHENSIVE INCOME (LOSS)</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Diluted</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>DilutedAverageShares</t>
-        </is>
-      </c>
+          <t>Basic $</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -26128,17 +26102,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H389" s="5" t="n">
-        <v>69.93377099999999</v>
-      </c>
-      <c r="I389" s="5" t="n">
-        <v>77.521216</v>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J389" s="5" t="n">
-        <v>89.725553</v>
+        <v>-3e-05</v>
       </c>
       <c r="K389" s="5" t="n">
-        <v>106.023171</v>
+        <v>1e-05</v>
       </c>
       <c r="L389" t="inlineStr">
         <is>
@@ -26154,19 +26132,15 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>OTHER COMPREHENSIVE INCOME (LOSS)</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>General and administrative expenses 23</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Diluted $</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -26187,16 +26161,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I390" s="5" t="n">
-        <v>8.445</v>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J390" s="5" t="n">
-        <v>12.974</v>
-      </c>
-      <c r="K390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3e-05</v>
+      </c>
+      <c r="K390" s="5" t="n">
+        <v>1e-05</v>
       </c>
       <c r="L390" t="inlineStr">
         <is>
@@ -26212,15 +26186,19 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Transaction costs 19</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr"/>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E391" t="inlineStr">
         <is>
           <t>-</t>
@@ -26236,21 +26214,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H391" s="5" t="n">
+        <v>69.93377099999999</v>
       </c>
       <c r="I391" s="5" t="n">
-        <v>0.835</v>
+        <v>77.521216</v>
       </c>
       <c r="J391" s="5" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="K391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>89.725553</v>
+      </c>
+      <c r="K391" s="5" t="n">
+        <v>101.921092</v>
       </c>
       <c r="L391" t="inlineStr">
         <is>
@@ -26266,17 +26240,17 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Finance income 24</t>
+          <t>Diluted</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>DilutedAverageShares</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -26294,21 +26268,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H392" s="5" t="n">
+        <v>69.93377099999999</v>
       </c>
       <c r="I392" s="5" t="n">
-        <v>-0.463</v>
+        <v>77.521216</v>
       </c>
       <c r="J392" s="5" t="n">
-        <v>-1.748</v>
-      </c>
-      <c r="K392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>89.725553</v>
+      </c>
+      <c r="K392" s="5" t="n">
+        <v>106.023171</v>
       </c>
       <c r="L392" t="inlineStr">
         <is>
@@ -26329,10 +26299,14 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Finance expense 24</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr"/>
+          <t>General and administrative expenses 23</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -26354,10 +26328,10 @@
         </is>
       </c>
       <c r="I393" s="5" t="n">
-        <v>8.558999999999999</v>
+        <v>8.445</v>
       </c>
       <c r="J393" s="5" t="n">
-        <v>7.832</v>
+        <v>12.974</v>
       </c>
       <c r="K393" t="inlineStr">
         <is>
@@ -26383,14 +26357,10 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) loss</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Transaction costs 19</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -26401,17 +26371,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G394" s="5" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="H394" s="5" t="n">
-        <v>-0.399</v>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I394" s="5" t="n">
-        <v>0.274</v>
+        <v>0.835</v>
       </c>
       <c r="J394" s="5" t="n">
-        <v>-10.306</v>
+        <v>0.716</v>
       </c>
       <c r="K394" t="inlineStr">
         <is>
@@ -26437,10 +26411,14 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Remeasurement of MDC secured note and stream obligation 19</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr"/>
+          <t>Finance income 24</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -26462,10 +26440,10 @@
         </is>
       </c>
       <c r="I395" s="5" t="n">
-        <v>0.978</v>
+        <v>-0.463</v>
       </c>
       <c r="J395" s="5" t="n">
-        <v>3.889</v>
+        <v>-1.748</v>
       </c>
       <c r="K395" t="inlineStr">
         <is>
@@ -26491,7 +26469,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Remeasurement of MDN stream obligation 14</t>
+          <t>Finance expense 24</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -26515,13 +26493,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I396" s="5" t="n">
+        <v>8.558999999999999</v>
       </c>
       <c r="J396" s="5" t="n">
-        <v>-4.5</v>
+        <v>7.832</v>
       </c>
       <c r="K396" t="inlineStr">
         <is>
@@ -26547,7 +26523,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Other expense</t>
+          <t>Foreign exchange (gain) loss</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -26565,19 +26541,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G397" s="5" t="n">
+        <v>0.643</v>
       </c>
       <c r="H397" s="5" t="n">
-        <v>1.56</v>
+        <v>-0.399</v>
       </c>
       <c r="I397" s="5" t="n">
-        <v>1.649</v>
+        <v>0.274</v>
       </c>
       <c r="J397" s="5" t="n">
-        <v>1.562</v>
+        <v>-10.306</v>
       </c>
       <c r="K397" t="inlineStr">
         <is>
@@ -26603,7 +26577,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>OTHER EXPENSES (INCOME)</t>
+          <t>Remeasurement of MDC secured note and stream obligation 19</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -26628,10 +26602,10 @@
         </is>
       </c>
       <c r="I398" s="5" t="n">
-        <v>11.832</v>
+        <v>0.978</v>
       </c>
       <c r="J398" s="5" t="n">
-        <v>-2.555</v>
+        <v>3.889</v>
       </c>
       <c r="K398" t="inlineStr">
         <is>
@@ -26657,14 +26631,10 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>INCOME (LOSS) BEFORE INCOME TAXES $</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Remeasurement of MDN stream obligation 14</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -26680,14 +26650,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H399" s="5" t="n">
-        <v>-4.697</v>
-      </c>
-      <c r="I399" s="5" t="n">
-        <v>-0.8179999999999999</v>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J399" s="5" t="n">
-        <v>3.4</v>
+        <v>-4.5</v>
       </c>
       <c r="K399" t="inlineStr">
         <is>
@@ -26713,10 +26687,14 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Deferred tax expense 30</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr"/>
+          <t>Other expense</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
@@ -26732,16 +26710,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H400" s="5" t="n">
+        <v>1.56</v>
       </c>
       <c r="I400" s="5" t="n">
-        <v>-3.009</v>
+        <v>1.649</v>
       </c>
       <c r="J400" s="5" t="n">
-        <v>-7.701</v>
+        <v>1.562</v>
       </c>
       <c r="K400" t="inlineStr">
         <is>
@@ -26767,14 +26743,10 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Income tax expense 30</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>OTHER EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr"/>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
@@ -26796,10 +26768,10 @@
         </is>
       </c>
       <c r="I401" s="5" t="n">
-        <v>-5.09</v>
+        <v>11.832</v>
       </c>
       <c r="J401" s="5" t="n">
-        <v>-10.153</v>
+        <v>-2.555</v>
       </c>
       <c r="K401" t="inlineStr">
         <is>
@@ -26825,12 +26797,12 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Loss for the period $</t>
+          <t>INCOME (LOSS) BEFORE INCOME TAXES $</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -26848,16 +26820,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H402" s="5" t="n">
+        <v>-4.697</v>
       </c>
       <c r="I402" s="5" t="n">
-        <v>-5.908</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="J402" s="5" t="n">
-        <v>-6.753</v>
+        <v>3.4</v>
       </c>
       <c r="K402" t="inlineStr">
         <is>
@@ -26878,12 +26848,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE INCOME</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Translation adjustment $</t>
+          <t>Deferred tax expense 30</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -26908,10 +26878,10 @@
         </is>
       </c>
       <c r="I403" s="5" t="n">
-        <v>1.076</v>
+        <v>-3.009</v>
       </c>
       <c r="J403" s="5" t="n">
-        <v>3.52</v>
+        <v>-7.701</v>
       </c>
       <c r="K403" t="inlineStr">
         <is>
@@ -26932,15 +26902,19 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE INCOME</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
-        </is>
-      </c>
-      <c r="D404" t="inlineStr"/>
+          <t>Income tax expense 30</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -26962,10 +26936,10 @@
         </is>
       </c>
       <c r="I404" s="5" t="n">
-        <v>1.076</v>
+        <v>-5.09</v>
       </c>
       <c r="J404" s="5" t="n">
-        <v>3.52</v>
+        <v>-10.153</v>
       </c>
       <c r="K404" t="inlineStr">
         <is>
@@ -26986,15 +26960,19 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>OTHER COMPREHENSIVE INCOME</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Total comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr"/>
+          <t>Loss for the period $</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
@@ -27016,10 +26994,10 @@
         </is>
       </c>
       <c r="I405" s="5" t="n">
-        <v>-4.832</v>
+        <v>-5.908</v>
       </c>
       <c r="J405" s="5" t="n">
-        <v>-3.233</v>
+        <v>-6.753</v>
       </c>
       <c r="K405" t="inlineStr">
         <is>
@@ -27040,12 +27018,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
+          <t>OTHER COMPREHENSIVE INCOME</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Basic $</t>
+          <t>Translation adjustment $</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
@@ -27064,14 +27042,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H406" s="5" t="n">
-        <v>-9.000000000000001e-05</v>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I406" s="5" t="n">
-        <v>-8.000000000000001e-05</v>
+        <v>1.076</v>
       </c>
       <c r="J406" s="5" t="n">
-        <v>-8.000000000000001e-05</v>
+        <v>3.52</v>
       </c>
       <c r="K406" t="inlineStr">
         <is>
@@ -27092,12 +27072,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
+          <t>OTHER COMPREHENSIVE INCOME</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Diluted $</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
@@ -27116,14 +27096,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H407" s="5" t="n">
-        <v>-9.000000000000001e-05</v>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I407" s="5" t="n">
-        <v>-8.000000000000001e-05</v>
+        <v>1.076</v>
       </c>
       <c r="J407" s="5" t="n">
-        <v>-8.000000000000001e-05</v>
+        <v>3.52</v>
       </c>
       <c r="K407" t="inlineStr">
         <is>
@@ -27144,19 +27126,15 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>OTHER COMPREHENSIVE INCOME</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>General and administrative expenses 21</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Total comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
@@ -27172,16 +27150,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H408" s="5" t="n">
-        <v>9.492000000000001</v>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I408" s="5" t="n">
-        <v>8.445</v>
-      </c>
-      <c r="J408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.832</v>
+      </c>
+      <c r="J408" s="5" t="n">
+        <v>-3.233</v>
       </c>
       <c r="K408" t="inlineStr">
         <is>
@@ -27202,12 +27180,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>Basic and diluted loss per share</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Transaction costs 17</t>
+          <t>Basic $</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
@@ -27227,15 +27205,13 @@
         </is>
       </c>
       <c r="H409" s="5" t="n">
-        <v>0.105</v>
+        <v>-9.000000000000001e-05</v>
       </c>
       <c r="I409" s="5" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="J409" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.000000000000001e-05</v>
+      </c>
+      <c r="J409" s="5" t="n">
+        <v>-8.000000000000001e-05</v>
       </c>
       <c r="K409" t="inlineStr">
         <is>
@@ -27256,12 +27232,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>Basic and diluted loss per share</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Listing expense 6</t>
+          <t>Diluted $</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
@@ -27281,17 +27257,13 @@
         </is>
       </c>
       <c r="H410" s="5" t="n">
-        <v>1.511</v>
-      </c>
-      <c r="I410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-9.000000000000001e-05</v>
+      </c>
+      <c r="I410" s="5" t="n">
+        <v>-8.000000000000001e-05</v>
+      </c>
+      <c r="J410" s="5" t="n">
+        <v>-8.000000000000001e-05</v>
       </c>
       <c r="K410" t="inlineStr">
         <is>
@@ -27317,10 +27289,14 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Finance expense 22</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr"/>
+          <t>General and administrative expenses 21</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -27337,10 +27313,10 @@
         </is>
       </c>
       <c r="H411" s="5" t="n">
-        <v>6.129</v>
+        <v>9.492000000000001</v>
       </c>
       <c r="I411" s="5" t="n">
-        <v>8.096</v>
+        <v>8.445</v>
       </c>
       <c r="J411" t="inlineStr">
         <is>
@@ -27371,14 +27347,10 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Transaction costs 17</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -27395,10 +27367,10 @@
         </is>
       </c>
       <c r="H412" s="5" t="n">
-        <v>-0.399</v>
+        <v>0.105</v>
       </c>
       <c r="I412" s="5" t="n">
-        <v>0.274</v>
+        <v>0.835</v>
       </c>
       <c r="J412" t="inlineStr">
         <is>
@@ -27429,7 +27401,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Remeasurement of secured note and stream obligation 17</t>
+          <t>Listing expense 6</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
@@ -27448,13 +27420,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I413" s="5" t="n">
-        <v>0.978</v>
+      <c r="H413" s="5" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
@@ -27485,7 +27457,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Income and mining tax expense 28</t>
+          <t>Finance expense 22</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
@@ -27505,10 +27477,10 @@
         </is>
       </c>
       <c r="H414" s="5" t="n">
-        <v>-1.602</v>
+        <v>6.129</v>
       </c>
       <c r="I414" s="5" t="n">
-        <v>-2.081</v>
+        <v>8.096</v>
       </c>
       <c r="J414" t="inlineStr">
         <is>
@@ -27539,10 +27511,14 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Deferred tax expense 28</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr"/>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>
@@ -27558,13 +27534,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H415" s="5" t="n">
+        <v>-0.399</v>
       </c>
       <c r="I415" s="5" t="n">
-        <v>-3.009</v>
+        <v>0.274</v>
       </c>
       <c r="J415" t="inlineStr">
         <is>
@@ -27595,14 +27569,10 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Income tax expense 28</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Remeasurement of secured note and stream obligation 17</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -27618,11 +27588,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H416" s="5" t="n">
-        <v>-1.602</v>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I416" s="5" t="n">
-        <v>-5.09</v>
+        <v>0.978</v>
       </c>
       <c r="J416" t="inlineStr">
         <is>
@@ -27653,14 +27625,10 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Net loss for the period $</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Income and mining tax expense 28</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -27677,10 +27645,10 @@
         </is>
       </c>
       <c r="H417" s="5" t="n">
-        <v>-6.299</v>
+        <v>-1.602</v>
       </c>
       <c r="I417" s="5" t="n">
-        <v>-5.908</v>
+        <v>-2.081</v>
       </c>
       <c r="J417" t="inlineStr">
         <is>
@@ -27706,12 +27674,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>22.    FINANCE EXPENSE</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Note December 31, 2022 December</t>
+          <t>Deferred tax expense 28</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
@@ -27730,11 +27698,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H418" s="5" t="n">
-        <v>2.021</v>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I418" s="5" t="n">
-        <v>0.031</v>
+        <v>-3.009</v>
       </c>
       <c r="J418" t="inlineStr">
         <is>
@@ -27760,15 +27730,19 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Finance income</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Investment loss (income) $</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr"/>
+          <t>Income tax expense 28</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -27785,10 +27759,10 @@
         </is>
       </c>
       <c r="H419" s="5" t="n">
-        <v>-0.148</v>
+        <v>-1.602</v>
       </c>
       <c r="I419" s="5" t="n">
-        <v>-0.463</v>
+        <v>-5.09</v>
       </c>
       <c r="J419" t="inlineStr">
         <is>
@@ -27814,15 +27788,19 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Accretion of future consideration payable (i) 7 $</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr"/>
+          <t>Net loss for the period $</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -27839,10 +27817,10 @@
         </is>
       </c>
       <c r="H420" s="5" t="n">
-        <v>2.826</v>
+        <v>-6.299</v>
       </c>
       <c r="I420" s="5" t="n">
-        <v>2.174</v>
+        <v>-5.908</v>
       </c>
       <c r="J420" t="inlineStr">
         <is>
@@ -27868,12 +27846,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>22.    FINANCE EXPENSE</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Accretion of deferred revenue 14</t>
+          <t>Note December 31, 2022 December</t>
         </is>
       </c>
       <c r="D421" t="inlineStr"/>
@@ -27887,14 +27865,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G421" s="5" t="n">
-        <v>2.048</v>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H421" s="5" t="n">
-        <v>2.608</v>
+        <v>2.021</v>
       </c>
       <c r="I421" s="5" t="n">
-        <v>2.675</v>
+        <v>0.031</v>
       </c>
       <c r="J421" t="inlineStr">
         <is>
@@ -27920,12 +27900,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>Finance income</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Accretion on decommissioning and restoration provisions 13</t>
+          <t>Investment loss (income) $</t>
         </is>
       </c>
       <c r="D422" t="inlineStr"/>
@@ -27944,13 +27924,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H422" s="5" t="n">
+        <v>-0.148</v>
       </c>
       <c r="I422" s="5" t="n">
-        <v>0.197</v>
+        <v>-0.463</v>
       </c>
       <c r="J422" t="inlineStr">
         <is>
@@ -27981,7 +27959,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Interest on revolving prepayment facility 15b</t>
+          <t>Accretion of future consideration payable (i) 7 $</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
@@ -28001,10 +27979,10 @@
         </is>
       </c>
       <c r="H423" s="5" t="n">
-        <v>0.348</v>
+        <v>2.826</v>
       </c>
       <c r="I423" s="5" t="n">
-        <v>0.453</v>
+        <v>2.174</v>
       </c>
       <c r="J423" t="inlineStr">
         <is>
@@ -28035,7 +28013,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Interest on loans payable 15c, 15d</t>
+          <t>Accretion of deferred revenue 14</t>
         </is>
       </c>
       <c r="D424" t="inlineStr"/>
@@ -28049,18 +28027,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G424" s="5" t="n">
+        <v>2.048</v>
+      </c>
+      <c r="H424" s="5" t="n">
+        <v>2.608</v>
       </c>
       <c r="I424" s="5" t="n">
-        <v>1.472</v>
+        <v>2.675</v>
       </c>
       <c r="J424" t="inlineStr">
         <is>
@@ -28091,7 +28065,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Other interest costs</t>
+          <t>Accretion on decommissioning and restoration provisions 13</t>
         </is>
       </c>
       <c r="D425" t="inlineStr"/>
@@ -28116,7 +28090,7 @@
         </is>
       </c>
       <c r="I425" s="5" t="n">
-        <v>0.224</v>
+        <v>0.197</v>
       </c>
       <c r="J425" t="inlineStr">
         <is>
@@ -28147,7 +28121,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Interest on finance lease 15a</t>
+          <t>Interest on revolving prepayment facility 15b</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
@@ -28167,10 +28141,10 @@
         </is>
       </c>
       <c r="H426" s="5" t="n">
-        <v>0.492</v>
+        <v>0.348</v>
       </c>
       <c r="I426" s="5" t="n">
-        <v>1.163</v>
+        <v>0.453</v>
       </c>
       <c r="J426" t="inlineStr">
         <is>
@@ -28201,14 +28175,10 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Finance fees and bank charges</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Interest on loans payable 15c, 15d</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -28219,14 +28189,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G427" s="5" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="H427" s="5" t="n">
-        <v>0.003</v>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I427" s="5" t="n">
-        <v>0.201</v>
+        <v>1.472</v>
       </c>
       <c r="J427" t="inlineStr">
         <is>
@@ -28257,7 +28231,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Finance costs total</t>
+          <t>Other interest costs</t>
         </is>
       </c>
       <c r="D428" t="inlineStr"/>
@@ -28271,14 +28245,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G428" s="5" t="n">
-        <v>4.705</v>
-      </c>
-      <c r="H428" s="5" t="n">
-        <v>6.277</v>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I428" s="5" t="n">
-        <v>8.558999999999999</v>
+        <v>0.224</v>
       </c>
       <c r="J428" t="inlineStr">
         <is>
@@ -28309,14 +28287,10 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Net finance expense $</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>InterestExpenseNonOperating</t>
-        </is>
-      </c>
+          <t>Interest on finance lease 15a</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
           <t>-</t>
@@ -28327,14 +28301,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G429" s="5" t="n">
-        <v>4.517</v>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H429" s="5" t="n">
-        <v>6.129</v>
+        <v>0.492</v>
       </c>
       <c r="I429" s="5" t="n">
-        <v>8.096</v>
+        <v>1.163</v>
       </c>
       <c r="J429" t="inlineStr">
         <is>
@@ -28360,17 +28336,17 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>General and administrative expenses 20</t>
+          <t>Finance fees and bank charges</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -28384,15 +28360,13 @@
         </is>
       </c>
       <c r="G430" s="5" t="n">
-        <v>7.699</v>
+        <v>0.314</v>
       </c>
       <c r="H430" s="5" t="n">
-        <v>9.492000000000001</v>
-      </c>
-      <c r="I430" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003</v>
+      </c>
+      <c r="I430" s="5" t="n">
+        <v>0.201</v>
       </c>
       <c r="J430" t="inlineStr">
         <is>
@@ -28418,12 +28392,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Transaction costs</t>
+          <t>Finance costs total</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
@@ -28438,15 +28412,13 @@
         </is>
       </c>
       <c r="G431" s="5" t="n">
-        <v>0.849</v>
+        <v>4.705</v>
       </c>
       <c r="H431" s="5" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="I431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.277</v>
+      </c>
+      <c r="I431" s="5" t="n">
+        <v>8.558999999999999</v>
       </c>
       <c r="J431" t="inlineStr">
         <is>
@@ -28472,15 +28444,19 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Listing expense 5</t>
-        </is>
-      </c>
-      <c r="D432" t="inlineStr"/>
+          <t>Net finance expense $</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
           <t>-</t>
@@ -28491,18 +28467,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G432" s="5" t="n">
+        <v>4.517</v>
       </c>
       <c r="H432" s="5" t="n">
-        <v>1.511</v>
-      </c>
-      <c r="I432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.129</v>
+      </c>
+      <c r="I432" s="5" t="n">
+        <v>8.096</v>
       </c>
       <c r="J432" t="inlineStr">
         <is>
@@ -28533,10 +28505,14 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Finance expense 21</t>
-        </is>
-      </c>
-      <c r="D433" t="inlineStr"/>
+          <t>General and administrative expenses 20</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -28548,10 +28524,10 @@
         </is>
       </c>
       <c r="G433" s="5" t="n">
-        <v>4.517</v>
+        <v>7.699</v>
       </c>
       <c r="H433" s="5" t="n">
-        <v>6.129</v>
+        <v>9.492000000000001</v>
       </c>
       <c r="I433" t="inlineStr">
         <is>
@@ -28587,14 +28563,10 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>OTHER EXPENSES</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Transaction costs</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
           <t>-</t>
@@ -28606,10 +28578,10 @@
         </is>
       </c>
       <c r="G434" s="5" t="n">
-        <v>4.923</v>
+        <v>0.849</v>
       </c>
       <c r="H434" s="5" t="n">
-        <v>8.906000000000001</v>
+        <v>0.105</v>
       </c>
       <c r="I434" t="inlineStr">
         <is>
@@ -28645,14 +28617,10 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>LOSS BEFORE INCOME TAXES $</t>
-        </is>
-      </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Listing expense 5</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
           <t>-</t>
@@ -28663,11 +28631,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G435" s="5" t="n">
-        <v>-11.879</v>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H435" s="5" t="n">
-        <v>-4.697</v>
+        <v>1.511</v>
       </c>
       <c r="I435" t="inlineStr">
         <is>
@@ -28703,7 +28673,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Income and mining tax expense 27</t>
+          <t>Finance expense 21</t>
         </is>
       </c>
       <c r="D436" t="inlineStr"/>
@@ -28718,10 +28688,10 @@
         </is>
       </c>
       <c r="G436" s="5" t="n">
-        <v>-0.6899999999999999</v>
+        <v>4.517</v>
       </c>
       <c r="H436" s="5" t="n">
-        <v>-1.602</v>
+        <v>6.129</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
@@ -28757,12 +28727,12 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Net loss for the period</t>
+          <t>OTHER EXPENSES</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -28776,10 +28746,10 @@
         </is>
       </c>
       <c r="G437" s="5" t="n">
-        <v>-12.569</v>
+        <v>4.923</v>
       </c>
       <c r="H437" s="5" t="n">
-        <v>-6.299</v>
+        <v>8.906000000000001</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
@@ -28810,15 +28780,19 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>to profit or loss</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Translation adjustment $</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr"/>
+          <t>LOSS BEFORE INCOME TAXES $</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E438" t="inlineStr">
         <is>
           <t>-</t>
@@ -28830,10 +28804,10 @@
         </is>
       </c>
       <c r="G438" s="5" t="n">
-        <v>-2.383</v>
+        <v>-11.879</v>
       </c>
       <c r="H438" s="5" t="n">
-        <v>-1.367</v>
+        <v>-4.697</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
@@ -28864,12 +28838,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>to profit or loss</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Income and mining tax expense 27</t>
         </is>
       </c>
       <c r="D439" t="inlineStr"/>
@@ -28884,10 +28858,10 @@
         </is>
       </c>
       <c r="G439" s="5" t="n">
-        <v>-2.383</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="H439" s="5" t="n">
-        <v>-1.367</v>
+        <v>-1.602</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
@@ -28918,15 +28892,19 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>to profit or loss</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Total comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr"/>
+          <t>Net loss for the period</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E440" t="inlineStr">
         <is>
           <t>-</t>
@@ -28938,10 +28916,10 @@
         </is>
       </c>
       <c r="G440" s="5" t="n">
-        <v>-14.952</v>
+        <v>-12.569</v>
       </c>
       <c r="H440" s="5" t="n">
-        <v>-7.666</v>
+        <v>-6.299</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
@@ -28977,14 +28955,10 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Translation adjustment $</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr"/>
       <c r="E441" t="inlineStr">
         <is>
           <t>-</t>
@@ -28996,10 +28970,10 @@
         </is>
       </c>
       <c r="G441" s="5" t="n">
-        <v>-2.8e-07</v>
+        <v>-2.383</v>
       </c>
       <c r="H441" s="5" t="n">
-        <v>-9e-08</v>
+        <v>-1.367</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
@@ -29035,14 +29009,10 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr"/>
       <c r="E442" t="inlineStr">
         <is>
           <t>-</t>
@@ -29054,10 +29024,10 @@
         </is>
       </c>
       <c r="G442" s="5" t="n">
-        <v>44.784428</v>
+        <v>-2.383</v>
       </c>
       <c r="H442" s="5" t="n">
-        <v>69.93377099999999</v>
+        <v>-1.367</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
@@ -29088,12 +29058,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>21.    FINANCE EXPENSE</t>
+          <t>to profit or loss</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Note December 31, 2021 December</t>
+          <t>Total comprehensive loss $</t>
         </is>
       </c>
       <c r="D443" t="inlineStr"/>
@@ -29108,10 +29078,10 @@
         </is>
       </c>
       <c r="G443" s="5" t="n">
-        <v>2.02</v>
+        <v>-14.952</v>
       </c>
       <c r="H443" s="5" t="n">
-        <v>0.031</v>
+        <v>-7.666</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
@@ -29142,15 +29112,19 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Finance income</t>
+          <t>to profit or loss</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Investment income $</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr"/>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E444" t="inlineStr">
         <is>
           <t>-</t>
@@ -29162,10 +29136,10 @@
         </is>
       </c>
       <c r="G444" s="5" t="n">
-        <v>-0.188</v>
+        <v>-2.8e-07</v>
       </c>
       <c r="H444" s="5" t="n">
-        <v>-0.148</v>
+        <v>-9e-08</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
@@ -29196,15 +29170,19 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Finance income</t>
+          <t>to profit or loss</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Finance income total</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr"/>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E445" t="inlineStr">
         <is>
           <t>-</t>
@@ -29216,10 +29194,10 @@
         </is>
       </c>
       <c r="G445" s="5" t="n">
-        <v>-0.188</v>
+        <v>44.784428</v>
       </c>
       <c r="H445" s="5" t="n">
-        <v>-0.148</v>
+        <v>69.93377099999999</v>
       </c>
       <c r="I445" t="inlineStr">
         <is>
@@ -29250,12 +29228,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>21.    FINANCE EXPENSE</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Accretion of future consideration payable (i) 6 $</t>
+          <t>Note December 31, 2021 December</t>
         </is>
       </c>
       <c r="D446" t="inlineStr"/>
@@ -29270,10 +29248,10 @@
         </is>
       </c>
       <c r="G446" s="5" t="n">
-        <v>2.122</v>
+        <v>2.02</v>
       </c>
       <c r="H446" s="5" t="n">
-        <v>2.826</v>
+        <v>0.031</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
@@ -29304,12 +29282,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>Finance income</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Interest on revolving prepayment facility 15</t>
+          <t>Investment income $</t>
         </is>
       </c>
       <c r="D447" t="inlineStr"/>
@@ -29324,10 +29302,10 @@
         </is>
       </c>
       <c r="G447" s="5" t="n">
-        <v>0.211</v>
+        <v>-0.188</v>
       </c>
       <c r="H447" s="5" t="n">
-        <v>0.348</v>
+        <v>-0.148</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
@@ -29358,12 +29336,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>Finance income</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Interest on finance lease</t>
+          <t>Finance income total</t>
         </is>
       </c>
       <c r="D448" t="inlineStr"/>
@@ -29378,10 +29356,10 @@
         </is>
       </c>
       <c r="G448" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.188</v>
       </c>
       <c r="H448" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.148</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
@@ -29412,34 +29390,30 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Professional fees 9 $</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Accretion of future consideration payable (i) 6 $</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F449" s="5" t="n">
-        <v>0.061383</v>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G449" s="5" t="n">
-        <v>0.104859</v>
-      </c>
-      <c r="H449" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.122</v>
+      </c>
+      <c r="H449" s="5" t="n">
+        <v>2.826</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
@@ -29470,34 +29444,30 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Filing fees</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Interest on revolving prepayment facility 15</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F450" s="5" t="n">
-        <v>0.008619</v>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G450" s="5" t="n">
-        <v>0.011295</v>
-      </c>
-      <c r="H450" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.211</v>
+      </c>
+      <c r="H450" s="5" t="n">
+        <v>0.348</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
@@ -29528,34 +29498,30 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Finance costs</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Transfer agent fees</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Interest on finance lease</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F451" s="5" t="n">
-        <v>0.005431</v>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G451" s="5" t="n">
-        <v>0.007775</v>
-      </c>
-      <c r="H451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01</v>
+      </c>
+      <c r="H451" s="5" t="n">
+        <v>0.003</v>
       </c>
       <c r="I451" t="inlineStr">
         <is>
@@ -29591,12 +29557,12 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Office and general</t>
+          <t>Professional fees 9 $</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -29605,10 +29571,10 @@
         </is>
       </c>
       <c r="F452" s="5" t="n">
-        <v>0.002388</v>
+        <v>0.061383</v>
       </c>
       <c r="G452" s="5" t="n">
-        <v>0.002778</v>
+        <v>0.104859</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
@@ -29649,12 +29615,12 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
+          <t>Filing fees</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>ForeignExchangeTradingGains</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -29662,13 +29628,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F453" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F453" s="5" t="n">
+        <v>0.008619</v>
       </c>
       <c r="G453" s="5" t="n">
-        <v>0.005585</v>
+        <v>0.011295</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
@@ -29709,22 +29673,24 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Expense recovery 3, 10</t>
-        </is>
-      </c>
-      <c r="D454" t="inlineStr"/>
+          <t>Transfer agent fees</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F454" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F454" s="5" t="n">
+        <v>0.005431</v>
       </c>
       <c r="G454" s="5" t="n">
-        <v>-0.122719</v>
+        <v>0.007775</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
@@ -29765,12 +29731,12 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
+          <t>Office and general</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -29779,10 +29745,10 @@
         </is>
       </c>
       <c r="F455" s="5" t="n">
-        <v>-0.077821</v>
+        <v>0.002388</v>
       </c>
       <c r="G455" s="5" t="n">
-        <v>-0.009573</v>
+        <v>0.002778</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
@@ -29823,12 +29789,12 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Net loss per share - basic and diluted</t>
+          <t>Foreign exchange</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>ForeignExchangeTradingGains</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -29836,11 +29802,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F456" s="5" t="n">
-        <v>-1.3e-07</v>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G456" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.005585</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
@@ -29881,24 +29849,22 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Expense recovery 3, 10</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr"/>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F457" s="5" t="n">
-        <v>0.589651</v>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G457" s="5" t="n">
-        <v>0.594747</v>
+        <v>-0.122719</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
@@ -29932,23 +29898,31 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B458" t="inlineStr"/>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>December</t>
-        </is>
-      </c>
-      <c r="D458" t="inlineStr"/>
-      <c r="E458" s="5" t="n">
-        <v>0.002018</v>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F458" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G458" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.077821</v>
+      </c>
+      <c r="G458" s="5" t="n">
+        <v>-0.009573</v>
       </c>
       <c r="H458" t="inlineStr">
         <is>
@@ -29984,29 +29958,29 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Professional fees (note 8) $</t>
+          <t>Net loss per share - basic and diluted</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E459" s="5" t="n">
-        <v>0.026644</v>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F459" s="5" t="n">
-        <v>0.061383</v>
-      </c>
-      <c r="G459" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.3e-07</v>
+      </c>
+      <c r="G459" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
@@ -30042,29 +30016,29 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Filing fees</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E460" s="5" t="n">
-        <v>0.00769</v>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F460" s="5" t="n">
-        <v>0.008619</v>
-      </c>
-      <c r="G460" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.589651</v>
+      </c>
+      <c r="G460" s="5" t="n">
+        <v>0.594747</v>
       </c>
       <c r="H460" t="inlineStr">
         <is>
@@ -30098,28 +30072,18 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B461" t="inlineStr"/>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Transfer agent fees</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr"/>
+      <c r="E461" s="5" t="n">
+        <v>0.002018</v>
       </c>
       <c r="F461" s="5" t="n">
-        <v>0.005431</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G461" t="inlineStr">
         <is>
@@ -30165,19 +30129,19 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Office and general</t>
+          <t>Professional fees (note 8) $</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E462" s="5" t="n">
-        <v>0.000312</v>
+        <v>0.026644</v>
       </c>
       <c r="F462" s="5" t="n">
-        <v>0.002388</v>
+        <v>0.061383</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
@@ -30223,17 +30187,19 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 5)</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr"/>
+          <t>Filing fees</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E463" s="5" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="F463" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00769</v>
+      </c>
+      <c r="F463" s="5" t="n">
+        <v>0.008619</v>
       </c>
       <c r="G463" t="inlineStr">
         <is>
@@ -30279,19 +30245,21 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Net loss per share – basic and diluted $</t>
+          <t>Transfer agent fees</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E464" s="5" t="n">
-        <v>-1e-08</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F464" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.005431</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
@@ -30337,42 +30305,334 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
+          <t>Office and general</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E465" s="5" t="n">
+        <v>0.000312</v>
+      </c>
+      <c r="F465" s="5" t="n">
+        <v>0.002388</v>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Share-based compensation (note 5)</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr"/>
+      <c r="E466" s="5" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Net loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E467" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F467" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
           <t>Weighted average shares outstanding- basic and diluted</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr"/>
-      <c r="E465" s="5" t="n">
+      <c r="D468" t="inlineStr"/>
+      <c r="E468" s="5" t="n">
         <v>1.430921</v>
       </c>
-      <c r="F465" s="5" t="n">
+      <c r="F468" s="5" t="n">
         <v>4.9</v>
       </c>
-      <c r="G465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L465" t="inlineStr">
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Professional fees (note 7) $</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E469" s="5" t="n">
+        <v>0.026644</v>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E470" s="5" t="n">
+        <v>-0.07964599999999999</v>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
         <is>
           <t>-</t>
         </is>
